--- a/Assets/Data/Tables/Boss.xlsx
+++ b/Assets/Data/Tables/Boss.xlsx
@@ -76,23 +76,23 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="00B8A68C"/>
+        <color rgb="00BFBFBF"/>
       </left>
       <right style="thin">
-        <color rgb="00B8A68C"/>
+        <color rgb="00BFBFBF"/>
       </right>
       <top style="thin">
-        <color rgb="00B8A68C"/>
+        <color rgb="00BFBFBF"/>
       </top>
       <bottom style="thin">
-        <color rgb="00B8A68C"/>
+        <color rgb="00BFBFBF"/>
       </bottom>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -100,6 +100,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -465,20 +466,25 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:P8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="1" max="1"/>
+    <col width="10" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
-    <col width="14" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="40" customWidth="1" min="10" max="10"/>
-    <col width="40" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="7" customWidth="1" min="10" max="10"/>
+    <col width="7" customWidth="1" min="11" max="11"/>
+    <col width="9" customWidth="1" min="12" max="12"/>
+    <col width="10" customWidth="1" min="13" max="13"/>
+    <col width="10" customWidth="1" min="14" max="14"/>
+    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -504,35 +510,60 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>ability</t>
+          <t>gimmick</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>abilityValue</t>
+          <t>gimmickValue</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>gimmickInterval</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>color</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>reward</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>drop</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>gem</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>failGold</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>prefab</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>icon</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="K1" s="2" t="inlineStr">
+      <c r="P1" s="2" t="inlineStr">
         <is>
           <t>#memo</t>
         </is>
@@ -561,45 +592,70 @@
       </c>
       <c r="E2" s="3" t="inlineStr">
         <is>
+          <t>BossGimmick</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" s="3" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>long</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>int</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G2" s="3" t="inlineStr">
-        <is>
-          <t>long</t>
-        </is>
-      </c>
-      <c r="H2" s="3" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="I2" s="3" t="inlineStr">
+      <c r="N2" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="O2" s="3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="K2" s="3" t="n"/>
+      <c r="P2" s="3" t="n"/>
     </row>
-    <row r="3" ht="36" customHeight="1">
+    <row r="3" ht="48" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>고유 번호 (4001~4999)</t>
+          <t>고유 번호 (6001~6999). 나오는 순서 = 스테이지 10·20·30…</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>영문 식별자 (코드·리소스용, 표 안에서 유일)</t>
+          <t>영문 식별자 (PC판 Boss_Key)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -609,42 +665,347 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>체력 배율 (× 스테이지 체력 계수)</t>
+          <t>체력 배수. 보스 체력 = 100 × 이 값 × 스테이지 hpRate</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>능력 종류 키</t>
+          <t>기믹 (None / Heal / Purge / Split / Move)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>능력 수치</t>
+          <t>Heal: 회복 비율 / Split: 분신 체력(분열 순간 본체 체력 대비) / Move: 속도 px/초</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
         <is>
-          <t>처치 보상</t>
+          <t>Heal·Purge: 간격(초)</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>프리팹 경로 (Resources 기준)</t>
+          <t>임시 구분 색 (#rrggbb, PC판 색)</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
+          <t>처치 점수 (스테이지 rewardRate를 곱함)</t>
+        </is>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>처치 때 레전더리 버섯 수</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>처치 때 균사석 (지갑이 생기면 지급)</t>
+        </is>
+      </c>
+      <c r="L3" s="4" t="inlineStr">
+        <is>
+          <t>못 잡았을 때 그 판 골드 배율</t>
+        </is>
+      </c>
+      <c r="M3" s="4" t="inlineStr">
+        <is>
+          <t>보스 프리팹 (비우면 군락 버섯을 키워 색만 바꿈)</t>
+        </is>
+      </c>
+      <c r="N3" s="4" t="inlineStr">
+        <is>
           <t>아이콘 경로 (Resources 기준)</t>
         </is>
       </c>
-      <c r="J3" s="4" t="inlineStr">
-        <is>
-          <t>인게임 설명</t>
-        </is>
-      </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>기믹 설명 (PC판 문구)</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>기획 메모 (게임에서 읽지 않음)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>6001</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>king</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>대왕송이</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="n"/>
+      <c r="G4" s="5" t="n"/>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>#c9a27a</t>
+        </is>
+      </c>
+      <c r="I4" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="inlineStr">
+        <is>
+          <t>다른 보스보다 체력이 훨씬 높아요</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="inlineStr">
+        <is>
+          <t>PC판 Hp_Mul 1.0 (PC는 지역마다 ×10이 따로 붙어 그대로 못 씀). 10분 힘 기준: 보스 판 피해 49 × 0.85 × 기믹 보정 1.00 → 체력 42. 그림 버섯(PC): 송이버섯</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>6002</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>cleaner</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>숲 속의 청소부</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>0.797</v>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Heal</t>
+        </is>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" s="5" t="inlineStr">
+        <is>
+          <t>#7ad07a</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="inlineStr">
+        <is>
+          <t>3초마다 최대 체력의 3%를 회복해요</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="inlineStr">
+        <is>
+          <t>PC판 Hp_Mul 0.35 (PC는 지역마다 ×10이 따로 붙어 그대로 못 씀). 25분 힘 기준: 보스 판 피해 197 × 0.85 × 기믹 보정 0.83 → 체력 139. 그림 버섯(PC): 선녀낙엽버섯</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>6003</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>angel</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>죽음의 천사</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>3.072</v>
+      </c>
+      <c r="E6" s="5" t="inlineStr">
+        <is>
+          <t>Purge</t>
+        </is>
+      </c>
+      <c r="F6" s="5" t="n"/>
+      <c r="G6" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>#b48cff</t>
+        </is>
+      </c>
+      <c r="I6" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="inlineStr">
+        <is>
+          <t>2초마다 필드의 임시 수확기를 모두 없애요</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>PC판 Hp_Mul 65.0 (PC는 지역마다 ×10이 따로 붙어 그대로 못 씀). 45분 힘 기준: 보스 판 피해 1,251 × 0.85 × 기믹 보정 0.90 → 체력 957. 그림 버섯(PC): 독우산광대버섯</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>6004</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>phantom</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>환상 버섯</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>6.042</v>
+      </c>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>Split</t>
+        </is>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="G7" s="5" t="n"/>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>#ff6b6b</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="inlineStr">
+        <is>
+          <t>체력 66%·33%에서 분신을 불러요. 분신까지 모두 쓰러뜨려야 해요</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="inlineStr">
+        <is>
+          <t>PC판 Hp_Mul 400.0 (PC는 지역마다 ×10이 따로 붙어 그대로 못 씀). 67분 힘 기준: 보스 판 피해 9,563 × 0.85 × 기믹 보정 0.50 → 체력 4,064. 그림 버섯(PC): 광대버섯</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>6005</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>mover</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>움직이는 버섯</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>34.752</v>
+      </c>
+      <c r="E8" s="5" t="inlineStr">
+        <is>
+          <t>Move</t>
+        </is>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>260</v>
+      </c>
+      <c r="G8" s="5" t="n"/>
+      <c r="H8" s="5" t="inlineStr">
+        <is>
+          <t>#f2a64a</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="n">
+        <v>3000</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="inlineStr">
+        <is>
+          <t>쉴 새 없이 좌우로 움직여요</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="inlineStr">
+        <is>
+          <t>PC판 Hp_Mul 200.0 (PC는 지역마다 ×10이 따로 붙어 그대로 못 씀). 90분 힘 기준: 보스 판 피해 80,211 × 0.85 × 기믹 보정 0.80 → 체력 54,543. 그림 버섯(PC): 동충하초</t>
         </is>
       </c>
     </row>

--- a/Assets/Data/Tables/Boss.xlsx
+++ b/Assets/Data/Tables/Boss.xlsx
@@ -690,7 +690,7 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>처치 점수 (스테이지 rewardRate를 곱함)</t>
+          <t>처치 점수 추가분 (지금 0: 처치 보상은 골드 max(이번 판, 직전 일반 판) × 2, RoundBase.bossRewardMul)</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.351</v>
+        <v>0.128</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
         </is>
       </c>
       <c r="I4" s="5" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="J4" s="5" t="n">
         <v>30</v>
@@ -779,7 +779,7 @@
       </c>
       <c r="P4" s="5" t="inlineStr">
         <is>
-          <t>PC판 Hp_Mul 1.0 (PC는 지역마다 ×10이 따로 붙어 그대로 못 씀). 10분 힘 기준: 보스 판 피해 49 × 0.85 × 기믹 보정 1.00 → 체력 42. 그림 버섯(PC): 송이버섯</t>
+          <t>PC Hp_Mul 1.0. 2026-10-26 밸런스: 사람 첫 도전 실패 10% 목표 (D_med 2.05, s 0.56) · 사람 보스 피해 = 봇(SKILL 1.0) × 0.8 가정, 측정기 BalanceBot</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.797</v>
+        <v>0.502</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
@@ -817,7 +817,7 @@
         </is>
       </c>
       <c r="I5" s="5" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="J5" s="5" t="n">
         <v>30</v>
@@ -837,7 +837,7 @@
       </c>
       <c r="P5" s="5" t="inlineStr">
         <is>
-          <t>PC판 Hp_Mul 0.35 (PC는 지역마다 ×10이 따로 붙어 그대로 못 씀). 25분 힘 기준: 보스 판 피해 197 × 0.85 × 기믹 보정 0.83 → 체력 139. 그림 버섯(PC): 선녀낙엽버섯</t>
+          <t>PC Hp_Mul 0.41(10-23)/0.35. 실패 15% 목표 (D_med 1.94, s 0.64), 회복 실효 ×1.11 · 사람 보스 피해 = 봇(SKILL 1.0) × 0.8 가정, 측정기 BalanceBot</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>3.072</v>
+        <v>2.984</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -873,7 +873,7 @@
         </is>
       </c>
       <c r="I6" s="5" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="J6" s="5" t="n">
         <v>30</v>
@@ -893,7 +893,7 @@
       </c>
       <c r="P6" s="5" t="inlineStr">
         <is>
-          <t>PC판 Hp_Mul 65.0 (PC는 지역마다 ×10이 따로 붙어 그대로 못 씀). 45분 힘 기준: 보스 판 피해 1,251 × 0.85 × 기믹 보정 0.90 → 체력 957. 그림 버섯(PC): 독우산광대버섯</t>
+          <t>PC Hp_Mul 37(10-23)/65. 실패 40% 목표 (D_med 1.23, s 0.83) · 사람 보스 피해 = 봇(SKILL 1.0) × 0.8 가정, 측정기 BalanceBot</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>6.042</v>
+        <v>1.783</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="I7" s="5" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>30</v>
@@ -949,7 +949,7 @@
       </c>
       <c r="P7" s="5" t="inlineStr">
         <is>
-          <t>PC판 Hp_Mul 400.0 (PC는 지역마다 ×10이 따로 붙어 그대로 못 씀). 67분 힘 기준: 보스 판 피해 9,563 × 0.85 × 기믹 보정 0.50 → 체력 4,064. 그림 버섯(PC): 광대버섯</t>
+          <t>PC Hp_Mul 160(10-23)/400. 실패 45% 목표 (D_med 1.06, s 0.43), 분신 실효 ×1.97 · 사람 보스 피해 = 봇(SKILL 1.0) × 0.8 가정, 측정기 BalanceBot</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>34.752</v>
+        <v>16.215</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -985,7 +985,7 @@
         </is>
       </c>
       <c r="I8" s="5" t="n">
-        <v>3000</v>
+        <v>0</v>
       </c>
       <c r="J8" s="5" t="n">
         <v>30</v>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="P8" s="5" t="inlineStr">
         <is>
-          <t>PC판 Hp_Mul 200.0 (PC는 지역마다 ×10이 따로 붙어 그대로 못 씀). 90분 힘 기준: 보스 판 피해 80,211 × 0.85 × 기믹 보정 0.80 → 체력 54,543. 그림 버섯(PC): 동충하초</t>
+          <t>PC Hp_Mul 150(10-23)/200. 실패 55% 목표 (D_med 0.88, s 1.01) · 사람 보스 피해 = 봇(SKILL 1.0) × 0.8 가정, 측정기 BalanceBot</t>
         </is>
       </c>
     </row>

--- a/Assets/Data/Tables/Boss.xlsx
+++ b/Assets/Data/Tables/Boss.xlsx
@@ -705,7 +705,7 @@
       </c>
       <c r="L3" s="4" t="inlineStr">
         <is>
-          <t>못 잡았을 때 그 판 골드 배율</t>
+          <t>못 잡았을 때 그 판 골드 배율 (비우면 1). 2026-10-27 패배 패널티 없음 = 1</t>
         </is>
       </c>
       <c r="M3" s="4" t="inlineStr">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="D4" s="5" t="n">
-        <v>0.128</v>
+        <v>0.1809</v>
       </c>
       <c r="E4" s="5" t="inlineStr">
         <is>
@@ -768,7 +768,7 @@
         <v>10</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M4" s="5" t="n"/>
       <c r="N4" s="5" t="n"/>
@@ -779,7 +779,7 @@
       </c>
       <c r="P4" s="5" t="inlineStr">
         <is>
-          <t>PC Hp_Mul 1.0. 2026-10-26 밸런스: 사람 첫 도전 실패 10% 목표 (D_med 2.05, s 0.56) · 사람 보스 피해 = 봇(SKILL 1.0) × 0.8 가정, 측정기 BalanceBot</t>
+          <t>PC Hp_Mul 1.0. 2026-10-27 M2: 사람 모델(수입 ×0.6, 보스 피해 ×0.234) 캠페인 첫 도착 스킬로 실제 보스 판을 돌려 첫 시도 처치 90% 목표로 맞춤. 옛 값 0.128(10-26)은 e5f377e 전 바 폭 0 버그 상태로 잰 값이라 폐기.</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
         </is>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.502</v>
+        <v>0.5278</v>
       </c>
       <c r="E5" s="5" t="inlineStr">
         <is>
@@ -826,7 +826,7 @@
         <v>15</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M5" s="5" t="n"/>
       <c r="N5" s="5" t="n"/>
@@ -837,7 +837,7 @@
       </c>
       <c r="P5" s="5" t="inlineStr">
         <is>
-          <t>PC Hp_Mul 0.41(10-23)/0.35. 실패 15% 목표 (D_med 1.94, s 0.64), 회복 실효 ×1.11 · 사람 보스 피해 = 봇(SKILL 1.0) × 0.8 가정, 측정기 BalanceBot</t>
+          <t>PC Hp_Mul 0.41(10-23)/0.35. 2026-10-27 M2: 사람 모델(수입 ×0.6, 보스 피해 ×0.234) 캠페인 첫 도착 스킬로 실제 보스 판을 돌려 첫 시도 처치 85% 목표로 맞춤. 옛 값 0.502(10-26)은 e5f377e 전 바 폭 0 버그 상태로 잰 값이라 폐기.</t>
         </is>
       </c>
     </row>
@@ -856,7 +856,7 @@
         </is>
       </c>
       <c r="D6" s="5" t="n">
-        <v>2.984</v>
+        <v>1.52</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>20</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M6" s="5" t="n"/>
       <c r="N6" s="5" t="n"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="P6" s="5" t="inlineStr">
         <is>
-          <t>PC Hp_Mul 37(10-23)/65. 실패 40% 목표 (D_med 1.23, s 0.83) · 사람 보스 피해 = 봇(SKILL 1.0) × 0.8 가정, 측정기 BalanceBot</t>
+          <t>PC Hp_Mul 37(10-23)/65. 2026-10-27 M2: 사람 모델(수입 ×0.6, 보스 피해 ×0.234) 캠페인 첫 도착 스킬로 실제 보스 판을 돌려 첫 시도 처치 60% 목표로 맞춤. 옛 값 2.984(10-26)은 e5f377e 전 바 폭 0 버그 상태로 잰 값이라 폐기.</t>
         </is>
       </c>
     </row>
@@ -912,7 +912,7 @@
         </is>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1.783</v>
+        <v>1.5</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>25</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M7" s="5" t="n"/>
       <c r="N7" s="5" t="n"/>
@@ -949,7 +949,7 @@
       </c>
       <c r="P7" s="5" t="inlineStr">
         <is>
-          <t>PC Hp_Mul 160(10-23)/400. 실패 45% 목표 (D_med 1.06, s 0.43), 분신 실효 ×1.97 · 사람 보스 피해 = 봇(SKILL 1.0) × 0.8 가정, 측정기 BalanceBot</t>
+          <t>PC Hp_Mul 160(10-23)/400. 2026-10-27 M2: 사람 모델(수입 ×0.6, 보스 피해 ×0.234) 캠페인 첫 도착 스킬로 실제 보스 판을 돌려 첫 시도 처치 55% 목표로 맞춤. 3341(분신술) 없는 상태 기준 ~40% (있으면 거의 100%), 분신 실효 실제 판 ≈×2.1(ProbeBoss ×3.27은 안 맞음). 옛 값 1.783(10-26)은 e5f377e 전 바 폭 0 버그 상태로 잰 값이라 폐기.</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
         </is>
       </c>
       <c r="D8" s="5" t="n">
-        <v>16.215</v>
+        <v>14.84</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>30</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="M8" s="5" t="n"/>
       <c r="N8" s="5" t="n"/>
@@ -1005,7 +1005,7 @@
       </c>
       <c r="P8" s="5" t="inlineStr">
         <is>
-          <t>PC Hp_Mul 150(10-23)/200. 실패 55% 목표 (D_med 0.88, s 1.01) · 사람 보스 피해 = 봇(SKILL 1.0) × 0.8 가정, 측정기 BalanceBot</t>
+          <t>PC Hp_Mul 150(10-23)/200. 2026-10-27 M2: 사람 모델(수입 ×0.6, 보스 피해 ×0.234) 캠페인 첫 도착 스킬로 실제 보스 판을 돌려 첫 시도 처치 45% 목표로 맞춤. ★ 균사석으로 3339 4레벨 상태. 옛 값 16.215(10-26)은 e5f377e 전 바 폭 0 버그 상태로 잰 값이라 폐기.</t>
         </is>
       </c>
     </row>
